--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104516_W7.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104516_W7.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>L. FISCHER</t>
+          <t>D. DIEZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.5913</v>
+        <v>5.7872</v>
       </c>
       <c r="E2" t="n">
-        <v>3.5612</v>
+        <v>3.7636</v>
       </c>
       <c r="F2" t="n">
-        <v>1.0301</v>
+        <v>2.0236</v>
       </c>
       <c r="G2" t="n">
-        <v>3.045</v>
+        <v>3.7293</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9177999999999999</v>
+        <v>0.7952</v>
       </c>
       <c r="I2" t="n">
-        <v>2.1272</v>
+        <v>2.934</v>
       </c>
       <c r="J2" t="n">
-        <v>3.1875</v>
+        <v>4.1126</v>
       </c>
       <c r="K2" t="n">
-        <v>1.7694</v>
+        <v>1.3133</v>
       </c>
       <c r="L2" t="n">
-        <v>1.418</v>
+        <v>2.7993</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.1425</v>
+        <v>-0.3833</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.8516</v>
+        <v>-0.518</v>
       </c>
       <c r="O2" t="n">
-        <v>0.7091</v>
+        <v>0.1347</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6805</v>
+        <v>2.0487</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.361</v>
+        <v>-0.2276</v>
       </c>
       <c r="R2" t="n">
-        <v>2.0415</v>
+        <v>2.2763</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1588</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3206</v>
+        <v>-0.1214</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1618</v>
+        <v>0.1306</v>
       </c>
       <c r="V2" t="n">
-        <v>0.7071</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>1.4141</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.7071</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. DIEZ</t>
+          <t>L. FISCHER</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.4108</v>
+        <v>4.4668</v>
       </c>
       <c r="E3" t="n">
-        <v>2.5516</v>
+        <v>3.2406</v>
       </c>
       <c r="F3" t="n">
-        <v>1.8592</v>
+        <v>1.2262</v>
       </c>
       <c r="G3" t="n">
-        <v>3.7345</v>
+        <v>3.0501</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7892</v>
+        <v>0.9136</v>
       </c>
       <c r="I3" t="n">
-        <v>2.9453</v>
+        <v>2.1365</v>
       </c>
       <c r="J3" t="n">
-        <v>4.1515</v>
+        <v>3.1624</v>
       </c>
       <c r="K3" t="n">
-        <v>1.3263</v>
+        <v>1.7474</v>
       </c>
       <c r="L3" t="n">
-        <v>2.8252</v>
+        <v>1.415</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.417</v>
+        <v>-0.1124</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.5371</v>
+        <v>-0.8339</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1201</v>
+        <v>0.7215</v>
       </c>
       <c r="P3" t="n">
-        <v>2.0415</v>
+        <v>0.6829</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.2268</v>
+        <v>-1.3658</v>
       </c>
       <c r="R3" t="n">
-        <v>2.2683</v>
+        <v>2.0487</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.3652</v>
+        <v>0.0313</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.3731</v>
+        <v>0.039</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0078</v>
+        <v>-0.0077</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.7025</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.405</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="4">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4873</v>
+        <v>0.0726</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9768</v>
+        <v>-0.1675</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5106000000000001</v>
+        <v>0.2401</v>
       </c>
       <c r="G4" t="n">
-        <v>1.0304</v>
+        <v>1.031</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3001</v>
+        <v>0.3042</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7302999999999999</v>
+        <v>0.7268</v>
       </c>
       <c r="J4" t="n">
-        <v>1.4874</v>
+        <v>1.4592</v>
       </c>
       <c r="K4" t="n">
-        <v>1.309</v>
+        <v>1.296</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1785</v>
+        <v>0.1632</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.457</v>
+        <v>-0.4282</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.0089</v>
+        <v>-0.9918</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5518999999999999</v>
+        <v>0.5636</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R4" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S4" t="n">
-        <v>2.5496</v>
+        <v>1.1311</v>
       </c>
       <c r="T4" t="n">
-        <v>1.8238</v>
+        <v>0.7195</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7258</v>
+        <v>0.4116</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.7997</v>
+        <v>-1.792</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. DE SOUSA</t>
+          <t>J. AXEL GUDMUNDSSON</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.5067</v>
+        <v>-1.016</v>
       </c>
       <c r="E5" t="n">
-        <v>2.5665</v>
+        <v>-1.8378</v>
       </c>
       <c r="F5" t="n">
-        <v>-3.0732</v>
+        <v>0.8217</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.0151</v>
+        <v>0.2281</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7951</v>
+        <v>-1.413</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.8103</v>
+        <v>1.641</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9707</v>
+        <v>0.9419999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>0.8587</v>
+        <v>-1.4554</v>
       </c>
       <c r="L5" t="n">
-        <v>0.112</v>
+        <v>2.3974</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.9858</v>
+        <v>-0.7139</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0636</v>
+        <v>0.0424</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.9222</v>
+        <v>-0.7563</v>
       </c>
       <c r="P5" t="n">
-        <v>1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q5" t="n">
+        <v>-2.5039</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.3658</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.281</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.1111</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.1699</v>
+      </c>
+      <c r="V5" t="n">
+        <v>-0.387</v>
+      </c>
+      <c r="W5" t="n">
+        <v>-0.387</v>
+      </c>
+      <c r="X5" t="n">
         <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.1342</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1.2666</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1.8207</v>
-      </c>
-      <c r="U5" t="n">
-        <v>-0.5541</v>
-      </c>
-      <c r="V5" t="n">
-        <v>-2.8924</v>
-      </c>
-      <c r="W5" t="n">
-        <v>-0.2249</v>
-      </c>
-      <c r="X5" t="n">
-        <v>-2.6675</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. AXEL GUDMUNDSSON</t>
+          <t>J. SAMUELS JR</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.1865</v>
+        <v>-1.2623</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.7957</v>
+        <v>-1.2071</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6092</v>
+        <v>-0.0552</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2414</v>
+        <v>-0.928</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.4112</v>
+        <v>-0.9536</v>
       </c>
       <c r="I6" t="n">
-        <v>1.6525</v>
+        <v>0.0256</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9762</v>
+        <v>-0.7007</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.4413</v>
+        <v>-0.7379</v>
       </c>
       <c r="L6" t="n">
-        <v>2.4175</v>
+        <v>0.0372</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.7348</v>
+        <v>-0.2273</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0301</v>
+        <v>-0.2157</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.7649</v>
+        <v>-0.0116</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.1342</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.4952</v>
+        <v>-1.3658</v>
       </c>
       <c r="R6" t="n">
-        <v>1.361</v>
+        <v>0.9105</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0919</v>
+        <v>-0.9685</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1089</v>
+        <v>-0.2301</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0169</v>
+        <v>-0.7385</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.3856</v>
+        <v>1.0895</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.3856</v>
+        <v>1.0895</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Y. NZOSA</t>
+          <t>J. RUBIO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.2792</v>
+        <v>-1.3217</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3273</v>
+        <v>-0.2467</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.6065</v>
+        <v>-1.075</v>
       </c>
       <c r="G7" t="n">
-        <v>1.0259</v>
+        <v>0.4877</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7114</v>
+        <v>-0.0233</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3145</v>
+        <v>0.511</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5541</v>
+        <v>0.3992</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5541</v>
+        <v>0.0345</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>0.3647</v>
       </c>
       <c r="M7" t="n">
-        <v>0.4718</v>
+        <v>0.0886</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1573</v>
+        <v>-0.0578</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3145</v>
+        <v>0.1463</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.2268</v>
+        <v>0.4553</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>0.6829</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1071</v>
+        <v>-1.1752</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>-0.4182</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1071</v>
+        <v>-0.757</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.1853</v>
+        <v>-1.0895</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.1853</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. RUBIO</t>
+          <t>Y. NZOSA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.3988</v>
+        <v>-1.3997</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.3087</v>
+        <v>0.3239</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.0902</v>
+        <v>-1.7237</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4802</v>
+        <v>1.0254</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.0289</v>
+        <v>0.7095</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5091</v>
+        <v>0.3159</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4051</v>
+        <v>0.5516</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0346</v>
+        <v>0.5516</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3705</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0751</v>
+        <v>0.4738</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0636</v>
+        <v>0.1579</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1387</v>
+        <v>0.3159</v>
       </c>
       <c r="P8" t="n">
-        <v>0.4537</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6805</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.24</v>
+        <v>-0.0185</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4869</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.7531</v>
+        <v>-0.0185</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.0927</v>
+        <v>-2.1789</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.0927</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. SAMUELS JR</t>
+          <t>S. DE SOUSA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.5751</v>
+        <v>-1.6536</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.3828</v>
+        <v>1.327</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1923</v>
+        <v>-2.9806</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.9365</v>
+        <v>-0.0125</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.9553</v>
+        <v>0.7901</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0187</v>
+        <v>-0.8026</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.6971000000000001</v>
+        <v>0.9596</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.7344000000000001</v>
+        <v>0.8479</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0373</v>
+        <v>0.1117</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.2395</v>
+        <v>-0.972</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2209</v>
+        <v>-0.0578</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.0186</v>
+        <v>-0.9143</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.4537</v>
+        <v>1.1382</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.361</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9073</v>
+        <v>1.1382</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.2775</v>
+        <v>0.1021</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4174</v>
+        <v>0.5966</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.8602</v>
+        <v>-0.4945</v>
       </c>
       <c r="V9" t="n">
-        <v>1.0927</v>
+        <v>-2.8814</v>
       </c>
       <c r="W9" t="n">
-        <v>1.0927</v>
+        <v>-0.2292</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-2.6522</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.9537</v>
+        <v>-2.457</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.2056</v>
+        <v>-2.404</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2519</v>
+        <v>-0.053</v>
       </c>
       <c r="G10" t="n">
-        <v>0.7673</v>
+        <v>0.7633</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.2985</v>
+        <v>-1.3091</v>
       </c>
       <c r="I10" t="n">
-        <v>2.0658</v>
+        <v>2.0723</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2172</v>
+        <v>0.1861</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.825</v>
+        <v>-0.8488</v>
       </c>
       <c r="L10" t="n">
-        <v>1.0422</v>
+        <v>1.035</v>
       </c>
       <c r="M10" t="n">
-        <v>0.5502</v>
+        <v>0.5770999999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.4735</v>
+        <v>-0.4603</v>
       </c>
       <c r="O10" t="n">
-        <v>1.0237</v>
+        <v>1.0374</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R10" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.3335</v>
+        <v>-0.8349</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.113</v>
+        <v>-0.2652</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2205</v>
+        <v>-0.5697</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
       <c r="W10" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.3461</v>
+        <v>-2.3367</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.3171</v>
+        <v>-2.5776</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.8128</v>
+        <v>-2.212</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.5043</v>
+        <v>-0.3655</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.7159</v>
+        <v>-1.7305</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.5857</v>
+        <v>-0.5968</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.1302</v>
+        <v>-1.1338</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.827</v>
+        <v>-0.8734</v>
       </c>
       <c r="K11" t="n">
-        <v>0.266</v>
+        <v>0.2371</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.093</v>
+        <v>-1.1105</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.8888</v>
+        <v>-0.8571</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.8516</v>
+        <v>-0.8339</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.0372</v>
+        <v>-0.0232</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.722</v>
+        <v>-2.7316</v>
       </c>
       <c r="R11" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2156</v>
+        <v>0.54</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5172</v>
+        <v>0.1457</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3015</v>
+        <v>0.3942</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.9317</v>
       </c>
       <c r="W11" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.7506</v>
+        <v>-4.4181</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.1618</v>
+        <v>-2.8782</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.5888</v>
+        <v>-1.5398</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.9802</v>
+        <v>-2.9861</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1385</v>
+        <v>0.1379</v>
       </c>
       <c r="I12" t="n">
-        <v>-3.1187</v>
+        <v>-3.124</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.4662</v>
+        <v>-2.4878</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0448</v>
+        <v>0.0377</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.511</v>
+        <v>-2.5255</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.514</v>
+        <v>-0.4982</v>
       </c>
       <c r="N12" t="n">
-        <v>0.09370000000000001</v>
+        <v>0.1002</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.6077</v>
+        <v>-0.5984</v>
       </c>
       <c r="P12" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R12" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.3583</v>
+        <v>-1.0254</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4688</v>
+        <v>-0.1628</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.8895</v>
+        <v>-0.8626</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="13">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.478299999999999</v>
+        <v>-5.779399999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.684</v>
+        <v>-2.2982</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.7943</v>
+        <v>-3.4812</v>
       </c>
       <c r="G13" t="n">
-        <v>4.677000000000001</v>
+        <v>4.657799999999998</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.6275000000000002</v>
+        <v>-0.6452999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>5.304199999999998</v>
+        <v>5.3027</v>
       </c>
       <c r="J13" t="n">
-        <v>7.9594</v>
+        <v>7.710799999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>3.1622</v>
+        <v>3.0234</v>
       </c>
       <c r="L13" t="n">
-        <v>4.797199999999999</v>
+        <v>4.687499999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>-3.2823</v>
+        <v>-3.0529</v>
       </c>
       <c r="N13" t="n">
-        <v>-3.7897</v>
+        <v>-3.6687</v>
       </c>
       <c r="O13" t="n">
-        <v>0.5074</v>
+        <v>0.6155999999999999</v>
       </c>
       <c r="P13" t="n">
-        <v>1.1341</v>
+        <v>1.1381</v>
       </c>
       <c r="Q13" t="n">
-        <v>-14.7441</v>
+        <v>-14.7959</v>
       </c>
       <c r="R13" t="n">
-        <v>15.8782</v>
+        <v>15.9342</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.6161</v>
+        <v>-1.9277</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3024000000000002</v>
+        <v>0.4142</v>
       </c>
       <c r="U13" t="n">
-        <v>-2.3139</v>
+        <v>-2.3422</v>
       </c>
       <c r="V13" t="n">
-        <v>-9.673299999999999</v>
+        <v>-9.647399999999999</v>
       </c>
       <c r="W13" t="n">
-        <v>4.4031</v>
+        <v>4.3728</v>
       </c>
       <c r="X13" t="n">
-        <v>-14.0764</v>
+        <v>-14.0202</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>R. LUZ</t>
+          <t>S. EVANS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.907</v>
+        <v>7.3116</v>
       </c>
       <c r="E14" t="n">
-        <v>3.7944</v>
+        <v>7.903</v>
       </c>
       <c r="F14" t="n">
-        <v>3.1126</v>
+        <v>-0.5914</v>
       </c>
       <c r="G14" t="n">
-        <v>4.749</v>
+        <v>4.8227</v>
       </c>
       <c r="H14" t="n">
-        <v>1.7342</v>
+        <v>1.4162</v>
       </c>
       <c r="I14" t="n">
-        <v>3.0148</v>
+        <v>3.4065</v>
       </c>
       <c r="J14" t="n">
-        <v>2.8612</v>
+        <v>6.8547</v>
       </c>
       <c r="K14" t="n">
-        <v>0.3983</v>
+        <v>2.7816</v>
       </c>
       <c r="L14" t="n">
-        <v>2.4629</v>
+        <v>4.073</v>
       </c>
       <c r="M14" t="n">
-        <v>1.8878</v>
+        <v>-2.032</v>
       </c>
       <c r="N14" t="n">
-        <v>1.336</v>
+        <v>-1.3654</v>
       </c>
       <c r="O14" t="n">
-        <v>0.5518999999999999</v>
+        <v>-0.6665</v>
       </c>
       <c r="P14" t="n">
-        <v>0.2268</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.1342</v>
+        <v>-3.4145</v>
       </c>
       <c r="R14" t="n">
-        <v>1.361</v>
+        <v>2.5039</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.0935</v>
+        <v>0.5179</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1179</v>
+        <v>0.4918</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0245</v>
+        <v>0.0261</v>
       </c>
       <c r="V14" t="n">
-        <v>2.0246</v>
+        <v>2.8814</v>
       </c>
       <c r="W14" t="n">
-        <v>2.1853</v>
+        <v>3.9709</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.1607</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S. EVANS</t>
+          <t>R. LUZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.1559</v>
+        <v>7.1657</v>
       </c>
       <c r="E15" t="n">
-        <v>7.267</v>
+        <v>3.8968</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.111</v>
+        <v>3.2688</v>
       </c>
       <c r="G15" t="n">
-        <v>4.8332</v>
+        <v>4.7668</v>
       </c>
       <c r="H15" t="n">
-        <v>1.4214</v>
+        <v>1.7456</v>
       </c>
       <c r="I15" t="n">
-        <v>3.4118</v>
+        <v>3.0212</v>
       </c>
       <c r="J15" t="n">
-        <v>6.9051</v>
+        <v>2.8541</v>
       </c>
       <c r="K15" t="n">
-        <v>2.8084</v>
+        <v>0.3964</v>
       </c>
       <c r="L15" t="n">
-        <v>4.0967</v>
+        <v>2.4576</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.0719</v>
+        <v>1.9128</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.387</v>
+        <v>1.3492</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.6849</v>
+        <v>0.5636</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.9073</v>
+        <v>0.2276</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.4025</v>
+        <v>-1.1382</v>
       </c>
       <c r="R15" t="n">
-        <v>2.4952</v>
+        <v>1.3658</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.6623</v>
+        <v>0.15</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2208</v>
+        <v>0.0019</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4416</v>
+        <v>0.1481</v>
       </c>
       <c r="V15" t="n">
-        <v>2.8924</v>
+        <v>2.0212</v>
       </c>
       <c r="W15" t="n">
-        <v>3.9851</v>
+        <v>2.1789</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.0927</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="16">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.7196</v>
+        <v>3.6836</v>
       </c>
       <c r="E16" t="n">
-        <v>2.161</v>
+        <v>1.8777</v>
       </c>
       <c r="F16" t="n">
-        <v>1.5586</v>
+        <v>1.8059</v>
       </c>
       <c r="G16" t="n">
-        <v>1.4115</v>
+        <v>1.4058</v>
       </c>
       <c r="H16" t="n">
-        <v>1.5341</v>
+        <v>1.5201</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1225</v>
+        <v>-0.1143</v>
       </c>
       <c r="J16" t="n">
-        <v>1.2855</v>
+        <v>1.2591</v>
       </c>
       <c r="K16" t="n">
-        <v>1.1735</v>
+        <v>1.1474</v>
       </c>
       <c r="L16" t="n">
-        <v>0.112</v>
+        <v>0.1117</v>
       </c>
       <c r="M16" t="n">
-        <v>0.126</v>
+        <v>0.1467</v>
       </c>
       <c r="N16" t="n">
-        <v>0.3605</v>
+        <v>0.3727</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.2345</v>
+        <v>-0.226</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2894</v>
+        <v>-0.3077</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0907</v>
+        <v>-0.1443</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3802</v>
+        <v>-0.1634</v>
       </c>
       <c r="V16" t="n">
-        <v>3.278</v>
+        <v>3.2684</v>
       </c>
       <c r="W16" t="n">
-        <v>3.0531</v>
+        <v>3.0392</v>
       </c>
       <c r="X16" t="n">
-        <v>0.2249</v>
+        <v>0.2292</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. UDEZE</t>
+          <t>R. GUERRERO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.464</v>
+        <v>1.6796</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6185</v>
+        <v>1.6476</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8455</v>
+        <v>0.0321</v>
       </c>
       <c r="G17" t="n">
-        <v>1.4428</v>
+        <v>0.0305</v>
       </c>
       <c r="H17" t="n">
-        <v>1.3868</v>
+        <v>0.0228</v>
       </c>
       <c r="I17" t="n">
-        <v>0.056</v>
+        <v>0.0077</v>
       </c>
       <c r="J17" t="n">
-        <v>1.7299</v>
+        <v>1.2763</v>
       </c>
       <c r="K17" t="n">
-        <v>1.6553</v>
+        <v>0.5688</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0746</v>
+        <v>0.7075</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.2871</v>
+        <v>-1.2458</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.2685</v>
+        <v>-0.546</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.0186</v>
+        <v>-0.6998</v>
       </c>
       <c r="P17" t="n">
-        <v>-2.9488</v>
+        <v>0.9105</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.4025</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.4537</v>
+        <v>0.9105</v>
       </c>
       <c r="S17" t="n">
-        <v>2.97</v>
+        <v>0.1939</v>
       </c>
       <c r="T17" t="n">
-        <v>2.6767</v>
+        <v>0.2135</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2934</v>
+        <v>-0.0196</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.5447</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.3856</v>
+        <v>0.1578</v>
       </c>
       <c r="X17" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R. GUERRERO</t>
+          <t>J. MCKOY</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.0716</v>
+        <v>0.3826</v>
       </c>
       <c r="E18" t="n">
-        <v>1.1811</v>
+        <v>-0.0635</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1095</v>
+        <v>0.4461</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0229</v>
+        <v>-1.8847</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0202</v>
+        <v>-3.1995</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0027</v>
+        <v>1.3149</v>
       </c>
       <c r="J18" t="n">
-        <v>1.2805</v>
+        <v>-1.8866</v>
       </c>
       <c r="K18" t="n">
-        <v>0.5715</v>
+        <v>-3.0551</v>
       </c>
       <c r="L18" t="n">
-        <v>0.709</v>
+        <v>1.1686</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.2576</v>
+        <v>0.0019</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.5513</v>
+        <v>-0.1444</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.7063</v>
+        <v>0.1463</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9073</v>
+        <v>1.5934</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9073</v>
+        <v>1.5934</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.405</v>
+        <v>0.8316</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2601</v>
+        <v>0.7336</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1449</v>
+        <v>0.098</v>
       </c>
       <c r="V18" t="n">
-        <v>0.5463</v>
+        <v>-0.1578</v>
       </c>
       <c r="W18" t="n">
-        <v>0.1607</v>
+        <v>1.0895</v>
       </c>
       <c r="X18" t="n">
-        <v>0.3856</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. MCKOY</t>
+          <t>M. UDEZE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.7091</v>
+        <v>-0.3092</v>
       </c>
       <c r="E19" t="n">
-        <v>0.202</v>
+        <v>-1.1737</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5071</v>
+        <v>0.8646</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.8758</v>
+        <v>1.4446</v>
       </c>
       <c r="H19" t="n">
-        <v>-3.2005</v>
+        <v>1.3817</v>
       </c>
       <c r="I19" t="n">
-        <v>1.3247</v>
+        <v>0.0629</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.8555</v>
+        <v>1.7152</v>
       </c>
       <c r="K19" t="n">
-        <v>-3.0415</v>
+        <v>1.6408</v>
       </c>
       <c r="L19" t="n">
-        <v>1.186</v>
+        <v>0.0745</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.0203</v>
+        <v>-0.2706</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.159</v>
+        <v>-0.259</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1387</v>
+        <v>-0.0116</v>
       </c>
       <c r="P19" t="n">
-        <v>1.5878</v>
+        <v>-2.9592</v>
       </c>
       <c r="Q19" t="n">
+        <v>-3.4145</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.4553</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1.2054</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0.9125</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0.2929</v>
+      </c>
+      <c r="V19" t="n">
         <v>0</v>
       </c>
-      <c r="R19" t="n">
-        <v>1.5878</v>
-      </c>
-      <c r="S19" t="n">
-        <v>1.1578</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0.9648</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0.1929</v>
-      </c>
-      <c r="V19" t="n">
-        <v>-0.1607</v>
-      </c>
       <c r="W19" t="n">
-        <v>1.0927</v>
+        <v>-0.387</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2534</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>C. ORTEGA</t>
+          <t>S. OKOYE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.0392</v>
+        <v>-1.8316</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2095</v>
+        <v>-3.9191</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.2487</v>
+        <v>2.0875</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.0887</v>
+        <v>-3.2754</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.4921</v>
+        <v>1.1223</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.5966</v>
+        <v>-4.3977</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.0798</v>
+        <v>-3.6236</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.4054</v>
+        <v>0.9653</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6744</v>
+        <v>-4.5889</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.0089</v>
+        <v>0.3482</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.0867</v>
+        <v>0.157</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.9222</v>
+        <v>0.1912</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.2268</v>
+        <v>0.9105</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9073</v>
+        <v>2.0487</v>
       </c>
       <c r="S20" t="n">
-        <v>1.2763</v>
+        <v>-0.0115</v>
       </c>
       <c r="T20" t="n">
-        <v>1.3308</v>
+        <v>-0.4046</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0544</v>
+        <v>0.3931</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.5447</v>
       </c>
       <c r="W20" t="n">
-        <v>1.0927</v>
+        <v>1.2472</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.0927</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="21">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.1972</v>
+        <v>-1.8835</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.0042</v>
+        <v>-1.6999</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.193</v>
+        <v>-0.1836</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.4993</v>
+        <v>-3.5038</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.8066</v>
+        <v>-1.8038</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.6927</v>
+        <v>-1.7</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.5019</v>
+        <v>-1.5428</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.5928</v>
+        <v>-0.6108</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.9091</v>
+        <v>-0.9320000000000001</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.9974</v>
+        <v>-1.961</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.2139</v>
+        <v>-1.1931</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.7835</v>
+        <v>-0.768</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R21" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1101</v>
+        <v>0.2137</v>
       </c>
       <c r="T21" t="n">
-        <v>0.127</v>
+        <v>0.485</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2371</v>
+        <v>-0.2713</v>
       </c>
       <c r="V21" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="W21" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2125,58 +2125,58 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.2817</v>
+        <v>-1.8893</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.1893</v>
+        <v>-2.8468</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9076</v>
+        <v>0.9575</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.8308</v>
+        <v>-1.8231</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.2555</v>
+        <v>-0.2502</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.5753</v>
+        <v>-1.5729</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.3595</v>
+        <v>-1.3669</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.6478</v>
+        <v>-0.6516999999999999</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.7117</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.4712</v>
+        <v>-0.4562</v>
       </c>
       <c r="N22" t="n">
-        <v>0.3923</v>
+        <v>0.4016</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.8636</v>
+        <v>-0.8578</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2241</v>
+        <v>0.1615</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6956</v>
+        <v>-0.3417</v>
       </c>
       <c r="U22" t="n">
-        <v>0.4715</v>
+        <v>0.5032</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S. OKOYE</t>
+          <t>C. ORTEGA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.3576</v>
+        <v>-2.6181</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.5929</v>
+        <v>-0.3918</v>
       </c>
       <c r="F23" t="n">
-        <v>2.2353</v>
+        <v>-2.2263</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.2808</v>
+        <v>-3.0802</v>
       </c>
       <c r="H23" t="n">
-        <v>1.1094</v>
+        <v>-1.488</v>
       </c>
       <c r="I23" t="n">
-        <v>-4.3902</v>
+        <v>-1.5922</v>
       </c>
       <c r="J23" t="n">
-        <v>-3.5991</v>
+        <v>-1.0884</v>
       </c>
       <c r="K23" t="n">
-        <v>0.9697</v>
+        <v>-0.4104</v>
       </c>
       <c r="L23" t="n">
-        <v>-4.5689</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="M23" t="n">
-        <v>0.3184</v>
+        <v>-1.9918</v>
       </c>
       <c r="N23" t="n">
-        <v>0.1397</v>
+        <v>-1.0775</v>
       </c>
       <c r="O23" t="n">
-        <v>0.1787</v>
+        <v>-0.9143</v>
       </c>
       <c r="P23" t="n">
-        <v>0.9073</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R23" t="n">
-        <v>2.0415</v>
+        <v>0.9105</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.5305</v>
+        <v>0.6897</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.113</v>
+        <v>0.7453</v>
       </c>
       <c r="U23" t="n">
-        <v>0.5825</v>
+        <v>-0.0556</v>
       </c>
       <c r="V23" t="n">
-        <v>0.5463</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.2534</v>
+        <v>1.0895</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.7071</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.6731</v>
+        <v>-4.4253</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.8527</v>
+        <v>-1.7491</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.8203</v>
+        <v>-2.6763</v>
       </c>
       <c r="G24" t="n">
         <v>-3.5611</v>
       </c>
       <c r="H24" t="n">
-        <v>0.176</v>
+        <v>0.178</v>
       </c>
       <c r="I24" t="n">
-        <v>-3.7371</v>
+        <v>-3.739</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.384</v>
+        <v>-1.3981</v>
       </c>
       <c r="K24" t="n">
-        <v>0.9005</v>
+        <v>0.8963</v>
       </c>
       <c r="L24" t="n">
-        <v>-2.2844</v>
+        <v>-2.2945</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.1771</v>
+        <v>-2.1629</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.7245</v>
+        <v>-0.7184</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.4526</v>
+        <v>-1.4446</v>
       </c>
       <c r="P24" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.473</v>
+        <v>-0.2301</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4688</v>
+        <v>-0.351</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0042</v>
+        <v>0.1209</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>6.478399999999997</v>
+        <v>7.266099999999998</v>
       </c>
       <c r="E25" t="n">
-        <v>3.794400000000002</v>
+        <v>3.481199999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>2.6842</v>
+        <v>3.7849</v>
       </c>
       <c r="G25" t="n">
-        <v>-4.677099999999999</v>
+        <v>-4.6579</v>
       </c>
       <c r="H25" t="n">
-        <v>0.6273999999999991</v>
+        <v>0.6452</v>
       </c>
       <c r="I25" t="n">
-        <v>-5.304399999999999</v>
+        <v>-5.302900000000001</v>
       </c>
       <c r="J25" t="n">
-        <v>3.2824</v>
+        <v>3.052999999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>3.789699999999999</v>
+        <v>3.6686</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.5073000000000003</v>
+        <v>-0.6155999999999999</v>
       </c>
       <c r="M25" t="n">
-        <v>-7.959299999999999</v>
+        <v>-7.710700000000001</v>
       </c>
       <c r="N25" t="n">
-        <v>-3.1624</v>
+        <v>-3.0233</v>
       </c>
       <c r="O25" t="n">
-        <v>-4.796899999999999</v>
+        <v>-4.6875</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.1341</v>
+        <v>-1.1381</v>
       </c>
       <c r="Q25" t="n">
-        <v>-15.8784</v>
+        <v>-15.9344</v>
       </c>
       <c r="R25" t="n">
-        <v>14.7441</v>
+        <v>14.796</v>
       </c>
       <c r="S25" t="n">
-        <v>2.6162</v>
+        <v>3.4144</v>
       </c>
       <c r="T25" t="n">
-        <v>2.313800000000001</v>
+        <v>2.342</v>
       </c>
       <c r="U25" t="n">
-        <v>0.3023999999999999</v>
+        <v>1.0724</v>
       </c>
       <c r="V25" t="n">
-        <v>9.6732</v>
+        <v>9.647300000000001</v>
       </c>
       <c r="W25" t="n">
-        <v>14.0764</v>
+        <v>14.0202</v>
       </c>
       <c r="X25" t="n">
-        <v>-4.4032</v>
+        <v>-4.3728</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104516_W7.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104516_W7.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104516_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104516_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-1.792</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104516_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104516_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104516_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104516_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104516_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-2.6522</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104516_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-2.3367</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104516_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104516_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104516_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-14.0202</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104516_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104516_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0.2292</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104516_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104516_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104516_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104516_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104516_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104516_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>0</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104516_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104516_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104516_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,7 @@
       <c r="X25" t="n">
         <v>-4.3728</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
